--- a/marketing_forms/015_mobile_experience_waitlist_form--marketing_forms.xlsx
+++ b/marketing_forms/015_mobile_experience_waitlist_form--marketing_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,23 +515,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>form_1</t>
+          <t>device_type</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Mobile Waitlist</t>
+          <t>Select the type of mobile device you are interested in</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>form_2</t>
+          <t>operating_system</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Waitlist</t>
+          <t>Which operating system do you currently use on your mobile device?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>form_3</t>
+          <t>interested_date</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mobile Device</t>
+          <t>When are you interested in experiencing mobile on your device?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>form_4</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Operating System</t>
+          <t>Provide your email address for updates and further information</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,40 +607,40 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>form_5</t>
+          <t>mobile_number</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Mobile Experience</t>
+          <t>Provide your mobile number for further contact</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>form_6</t>
+          <t>referral</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Interested Date</t>
+          <t>Who referred you to this form?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>form_7</t>
+          <t>additional_comments</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>Additional comments about your mobile experience interest</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>form_8</t>
+          <t>operating_system_version</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Which version of your operating system are you currently using?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>form_9</t>
+          <t>device_brand</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Mobile Number</t>
+          <t>What brand of mobile device do you have?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,366 +722,67 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>form_10</t>
+          <t>wait_time</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Referral</t>
+          <t>When would you like to receive your mobile experience?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>form_11</t>
+          <t>interest_level</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Additional Information</t>
+          <t>On a scale of 0-10, how much are you interested in getting a mobile experience?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>form_12</t>
+          <t>follow_up_info</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Waitlist</t>
+          <t>Any other information you'd like to share with us?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>form_13</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Interested In</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>form_14</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Mobile Number 2</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>form_15</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Referral 2</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>form_16</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Interested In 2</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>form_17</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Mobile Experience 2</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>form_18</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Interested Date 2</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>form_19</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Time 2</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>form_20</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Email 2</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>form_21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Mobile Number 2</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>form_22</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Waitlist 2</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>form_23</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Referral 2</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>form_24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Interested In 2</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>form_24</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Mobile Device 2</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,544 +827,272 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>form_2_choices</t>
+          <t>device_type_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>apple</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>apple</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>form_2_choices</t>
+          <t>device_type_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>google</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>google</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>form_2_choices</t>
+          <t>operating_system_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>ios</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>iOS</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>form_3_choices</t>
+          <t>operating_system_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>apple</t>
+          <t>android</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>apple</t>
+          <t>android</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>form_3_choices</t>
+          <t>operating_system_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>windows</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>windows</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>form_4_choices</t>
+          <t>referral_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ios</t>
+          <t>referral1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>iOS</t>
+          <t>referral1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>form_4_choices</t>
+          <t>referral_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>android</t>
+          <t>referral2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>android</t>
+          <t>referral2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>form_4_choices</t>
+          <t>referral_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>windows</t>
+          <t>referral3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>windows</t>
+          <t>referral3</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>form_10_choices</t>
+          <t>operating_system_version_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>referral1</t>
+          <t>ios_14</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>referral1</t>
+          <t>iOS 14</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>form_10_choices</t>
+          <t>operating_system_version_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>referral2</t>
+          <t>ios_15</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>referral2</t>
+          <t>iOS 15</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>form_10_choices</t>
+          <t>operating_system_version_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>referral3</t>
+          <t>android_10</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>referral3</t>
+          <t>Android 10</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>form_12_choices</t>
+          <t>operating_system_version_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>android_11</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>Android 11</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>form_12_choices</t>
+          <t>operating_system_version_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>windows_10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>Windows 10</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>form_12_choices</t>
+          <t>operating_system_version_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>option6</t>
+          <t>windows_11</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>option6</t>
+          <t>Windows 11</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>form_13_choices</t>
+          <t>device_brand_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>option7</t>
+          <t>apple</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>option7</t>
+          <t>Apple</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>form_13_choices</t>
+          <t>device_brand_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>option8</t>
+          <t>google</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>option8</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>form_13_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>option9</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>option9</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>form_15_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>referral4</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>referral4</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>form_15_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>referral5</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>referral5</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>form_15_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>referral6</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>referral6</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>form_16_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>option10</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>option10</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>form_16_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>option11</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>option11</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>form_16_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>option12</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>option12</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>form_22_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>option13</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>option13</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>form_22_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>option14</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>option14</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>form_23_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>referral7</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>referral7</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>form_23_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>referral8</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>referral8</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>form_24_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>option15</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>option15</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>form_24_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>option16</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>option16</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>form_24_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>option17</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>option17</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>form_24_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>option18</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>option18</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>form_24_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>option19</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>option19</t>
+          <t>Google</t>
         </is>
       </c>
     </row>
